--- a/Global_Mobility_Data.xlsx
+++ b/Global_Mobility_Data.xlsx
@@ -2,44 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd00e77f03af9673/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd00e77f03af9673/Desktop/Siemens/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC8A59BA-5CFD-48D8-AB85-24C330F2EA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D2BFD3505442AD55E9B1575600F673F5ED81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D2BD52-5ED7-4B25-B001-F40D5984F444}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{19254DB2-D22E-4E87-980B-8D8BBBA09602}"/>
+    <workbookView xWindow="33000" yWindow="3510" windowWidth="20745" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="98">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -65,6 +46,21 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Cost_Center</t>
+  </si>
+  <si>
+    <t>Visa_Status</t>
+  </si>
+  <si>
+    <t>Relocation_Allowance_EUR</t>
+  </si>
+  <si>
+    <t>Equity_Shares</t>
+  </si>
+  <si>
     <t>EMP001</t>
   </si>
   <si>
@@ -129,19 +125,217 @@
   </si>
   <si>
     <t>Brazil</t>
+  </si>
+  <si>
+    <t>EMP000</t>
+  </si>
+  <si>
+    <t>Mobility (MO)</t>
+  </si>
+  <si>
+    <t>CC-1907</t>
+  </si>
+  <si>
+    <t>Pending HR Approval</t>
+  </si>
+  <si>
+    <t>Germany (Erlangen/Munich)</t>
+  </si>
+  <si>
+    <t>Digital Industries</t>
+  </si>
+  <si>
+    <t>AC-1907</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>DE-1001</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>US-2001</t>
+  </si>
+  <si>
+    <t>Visa Sponsored</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>IN-3001</t>
+  </si>
+  <si>
+    <t>Supply Chain</t>
+  </si>
+  <si>
+    <t>CN-4001</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>UK-5001</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>DE-1002</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>US-2002</t>
+  </si>
+  <si>
+    <t>FR-6001</t>
+  </si>
+  <si>
+    <t>EU Citizen</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>IN-3002</t>
+  </si>
+  <si>
+    <t>Logistics</t>
+  </si>
+  <si>
+    <t>BR-7001</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>US-INT1</t>
+  </si>
+  <si>
+    <t>EMP011</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>ES-8001</t>
+  </si>
+  <si>
+    <t>EMP012</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>IT-9001</t>
+  </si>
+  <si>
+    <t>EMP013</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>NL-1101</t>
+  </si>
+  <si>
+    <t>EMP014</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>TR-1201</t>
+  </si>
+  <si>
+    <t>EMP015</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>PL-1301</t>
+  </si>
+  <si>
+    <t>EMP016</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>CA-1401</t>
+  </si>
+  <si>
+    <t>EMP017</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>AT-1501</t>
+  </si>
+  <si>
+    <t>EMP018</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>SE-1601</t>
+  </si>
+  <si>
+    <t>EMP019</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>CH-1701</t>
+  </si>
+  <si>
+    <t>EMP020</t>
+  </si>
+  <si>
+    <t>UAE</t>
+  </si>
+  <si>
+    <t>AE-1801</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,7 +346,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -160,19 +354,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -182,6 +396,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -195,44 +413,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -259,32 +477,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -311,24 +511,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -340,213 +522,238 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E61249A0-F0D8-4E77-989E-23E4399217CC}">
-  <dimension ref="A1:H11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>65000</v>
@@ -554,25 +761,40 @@
       <c r="E2">
         <v>5000</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>44941</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>45184</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2">
+        <v>2000</v>
+      </c>
+      <c r="M2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>110000</v>
@@ -580,25 +802,40 @@
       <c r="E3">
         <v>15000</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>44986</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>46082</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>10000</v>
+      </c>
+      <c r="M3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>45000</v>
@@ -606,25 +843,40 @@
       <c r="E4">
         <v>3000</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>45292</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>45657</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
       </c>
       <c r="D5">
         <v>85000</v>
@@ -632,25 +884,40 @@
       <c r="E5">
         <v>10000</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>44713</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>45809</v>
       </c>
       <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5">
+        <v>8000</v>
+      </c>
+      <c r="M5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
       </c>
       <c r="D6">
         <v>75000</v>
@@ -658,25 +925,40 @@
       <c r="E6">
         <v>6000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>45337</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>45519</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>3000</v>
+      </c>
+      <c r="M6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
       </c>
       <c r="D7">
         <v>55000</v>
@@ -684,25 +966,40 @@
       <c r="E7">
         <v>4000</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>45231</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>45597</v>
       </c>
       <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
       </c>
       <c r="D8">
         <v>95000</v>
@@ -710,25 +1007,40 @@
       <c r="E8">
         <v>8000</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>45056</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
         <v>45240</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8">
+        <v>4000</v>
+      </c>
+      <c r="M8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>80000</v>
@@ -736,25 +1048,40 @@
       <c r="E9">
         <v>9000</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <v>45383</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="2">
         <v>46478</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9">
+        <v>7000</v>
+      </c>
+      <c r="M9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>50000</v>
@@ -762,25 +1089,40 @@
       <c r="E10">
         <v>4000</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="2">
         <v>44409</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>45505</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10">
+        <v>2000</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>60000</v>
@@ -788,17 +1130,569 @@
       <c r="E11">
         <v>5000</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>45301</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>45453</v>
       </c>
       <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11">
+        <v>3000</v>
+      </c>
+      <c r="M11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>1600</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46143</v>
+      </c>
+      <c r="G12" s="2">
+        <v>46156</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12">
+        <v>1000</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1001907</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>1500</v>
+      </c>
+      <c r="E13">
+        <v>500</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46146</v>
+      </c>
+      <c r="G13" s="2">
+        <v>46146</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13">
+        <v>150</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>100907</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
         <v>15</v>
       </c>
+      <c r="D14">
+        <v>4000</v>
+      </c>
+      <c r="E14">
+        <v>500</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46146</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46146</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14">
+        <v>1500</v>
+      </c>
+      <c r="M14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>72000</v>
+      </c>
+      <c r="E16">
+        <v>8000</v>
+      </c>
+      <c r="F16" s="4">
+        <v>45444</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46539</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16">
+        <v>6000</v>
+      </c>
+      <c r="M16">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>68000</v>
+      </c>
+      <c r="E17">
+        <v>5500</v>
+      </c>
+      <c r="F17" s="4">
+        <v>45352</v>
+      </c>
+      <c r="G17" s="4">
+        <v>45536</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17">
+        <v>2500</v>
+      </c>
+      <c r="M17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18">
+        <v>90000</v>
+      </c>
+      <c r="E18">
+        <v>11000</v>
+      </c>
+      <c r="F18" s="4">
+        <v>45108</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46204</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18">
+        <v>9000</v>
+      </c>
+      <c r="M18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19">
+        <v>40000</v>
+      </c>
+      <c r="E19">
+        <v>2500</v>
+      </c>
+      <c r="F19" s="4">
+        <v>45292</v>
+      </c>
+      <c r="G19" s="4">
+        <v>45657</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <v>65000</v>
+      </c>
+      <c r="E20">
+        <v>7000</v>
+      </c>
+      <c r="F20" s="4">
+        <v>45170</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46266</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20">
+        <v>5000</v>
+      </c>
+      <c r="M20">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>95000</v>
+      </c>
+      <c r="E21">
+        <v>12000</v>
+      </c>
+      <c r="F21" s="4">
+        <v>45323</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46419</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21">
+        <v>8000</v>
+      </c>
+      <c r="M21">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>70000</v>
+      </c>
+      <c r="E22">
+        <v>6000</v>
+      </c>
+      <c r="F22" s="4">
+        <v>45413</v>
+      </c>
+      <c r="G22" s="4">
+        <v>45597</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" t="s">
+        <v>87</v>
+      </c>
+      <c r="K22" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22">
+        <v>2000</v>
+      </c>
+      <c r="M22">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>88000</v>
+      </c>
+      <c r="E23">
+        <v>9500</v>
+      </c>
+      <c r="F23" s="4">
+        <v>45200</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46296</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23" t="s">
+        <v>90</v>
+      </c>
+      <c r="K23" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23">
+        <v>7500</v>
+      </c>
+      <c r="M23">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24">
+        <v>120000</v>
+      </c>
+      <c r="E24">
+        <v>15000</v>
+      </c>
+      <c r="F24" s="4">
+        <v>45292</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46388</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>93</v>
+      </c>
+      <c r="J24" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" t="s">
+        <v>47</v>
+      </c>
+      <c r="L24">
+        <v>12000</v>
+      </c>
+      <c r="M24">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>85000</v>
+      </c>
+      <c r="E25">
+        <v>10000</v>
+      </c>
+      <c r="F25" s="4">
+        <v>45444</v>
+      </c>
+      <c r="G25" s="4">
+        <v>45627</v>
+      </c>
+      <c r="H25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25" t="s">
+        <v>47</v>
+      </c>
+      <c r="L25">
+        <v>5000</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>